--- a/data/trending_integrated_20261021_09.xlsx
+++ b/data/trending_integrated_20261021_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1273000</v>
+        <v>1290000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+4.09%</t>
+          <t>'+5.48%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G2" t="n">
-        <v>2680</v>
+        <v>2487</v>
       </c>
       <c r="H2" t="n">
         <v>48.77</v>
@@ -601,7 +601,7 @@
         <v>1260000</v>
       </c>
       <c r="L2" t="n">
-        <v>1274000</v>
+        <v>1291000</v>
       </c>
       <c r="M2" t="n">
         <v>1258000</v>
@@ -610,7 +610,7 @@
         <v>48.81</v>
       </c>
       <c r="O2" t="n">
-        <v>305396143000</v>
+        <v>662202788000</v>
       </c>
       <c r="P2" t="n">
         <v>2987000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 시간외 반도체 주가 급등과 AI 관련 투자 확대 소식으로 SK하이닉스 주가 상승 기대. 최태원 언급.</t>
+          <t>미국 시간 외 반도체 주가 급등 및 AI 데이터센터 투자 확대 뉴스에 따른 주가 상승 기대감 형성. 솔리다임 상장 철회 요구 등 일부 부정적 언급 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>218000</v>
+        <v>220500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+4.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G3" t="n">
-        <v>3619</v>
+        <v>3484</v>
       </c>
       <c r="H3" t="n">
         <v>46.08</v>
@@ -693,7 +693,7 @@
         <v>217000</v>
       </c>
       <c r="L3" t="n">
-        <v>219500</v>
+        <v>221000</v>
       </c>
       <c r="M3" t="n">
         <v>217000</v>
@@ -702,7 +702,7 @@
         <v>46.04</v>
       </c>
       <c r="O3" t="n">
-        <v>173906343750</v>
+        <v>399343725500</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 시간외 반도체 주가 급등에 따른 삼성전자 주가 상승 기대감. 이재명, 김용범 등 정치인 언급.</t>
+          <t>미국 시간 외 반도체 주가 급등 소식과 야간 선물 상승에 따른 주가 상승 기대감 형성. 그러나 정치적 이슈 언급으로 객관적 근거는 일부 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '시간외', '상승']</t>
+          <t>['반도체', '시간외', '선물']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14480</v>
+        <v>14650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.26%</t>
+          <t>'+3.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
         <v>9.82</v>
@@ -785,7 +785,7 @@
         <v>14340</v>
       </c>
       <c r="L4" t="n">
-        <v>14550</v>
+        <v>14760</v>
       </c>
       <c r="M4" t="n">
         <v>14340</v>
@@ -794,7 +794,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1273971440</v>
+        <v>4889835835</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치인(이재명) 및 공매도 관련 언급이 다수. 푸르지오 영화 개봉 언급.</t>
+          <t>정치적 이슈 및 공매도, 주가 조작 의혹 제기로 부정적인 논조 형성. 객관적 근거 없이 하락 기대감만 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '이재명']</t>
+          <t>['공매도', '주가조작', '대차']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -833,6 +833,98 @@
       <c r="Z4" t="inlineStr">
         <is>
           <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>63700</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+1.43%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>157</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>62800</v>
+      </c>
+      <c r="K5" t="n">
+        <v>63600</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64200</v>
+      </c>
+      <c r="M5" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12126904050</v>
+      </c>
+      <c r="P5" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMR 관련 뉴스 및 데이터센터 투자 확대 가능성에 대한 기대감 존재. 그러나 반도체 대비 낮은 상승률과 정부 정책 비판으로 객관성 부족.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['SMR', '데이터센터', '야간선물']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261021_09.xlsx
+++ b/data/trending_integrated_20261021_09.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1290000</v>
+        <v>1301000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+5.48%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G2" t="n">
-        <v>2487</v>
+        <v>2006</v>
       </c>
       <c r="H2" t="n">
         <v>48.77</v>
@@ -601,7 +601,7 @@
         <v>1260000</v>
       </c>
       <c r="L2" t="n">
-        <v>1291000</v>
+        <v>1304000</v>
       </c>
       <c r="M2" t="n">
         <v>1258000</v>
@@ -610,7 +610,7 @@
         <v>48.81</v>
       </c>
       <c r="O2" t="n">
-        <v>662202788000</v>
+        <v>930428350500</v>
       </c>
       <c r="P2" t="n">
         <v>2987000</v>
@@ -619,23 +619,23 @@
         <v>468000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 시간 외 반도체 주가 급등 및 AI 데이터센터 투자 확대 뉴스에 따른 주가 상승 기대감 형성. 솔리다임 상장 철회 요구 등 일부 부정적 언급 존재.</t>
+          <t>미국 시간외 반도체 주가 급등 소식에 SK하이닉스 상승 기대감 형성. 솔리다임 상장 관련 언급 및 정치적 발언이 혼재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '시간외']</t>
+          <t>['반도체', '솔리다임', '시간외']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220500</v>
+        <v>222500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.26%</t>
+          <t>'+5.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="G3" t="n">
-        <v>3484</v>
+        <v>3216</v>
       </c>
       <c r="H3" t="n">
         <v>46.08</v>
@@ -693,7 +693,7 @@
         <v>217000</v>
       </c>
       <c r="L3" t="n">
-        <v>221000</v>
+        <v>223000</v>
       </c>
       <c r="M3" t="n">
         <v>217000</v>
@@ -702,7 +702,7 @@
         <v>46.04</v>
       </c>
       <c r="O3" t="n">
-        <v>399343725500</v>
+        <v>592368928000</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -711,14 +711,14 @@
         <v>94500</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 시간 외 반도체 주가 급등 소식과 야간 선물 상승에 따른 주가 상승 기대감 형성. 그러나 정치적 이슈 언급으로 객관적 근거는 일부 혼재.</t>
+          <t>미국 시간외 반도체 주가 급등 및 실적 호조 소식에 따른 삼성전자 상승 기대감 형성. 다만, 일부 정치적 발언이 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '시간외', '선물']</t>
+          <t>['반도체', '시간외', '실적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14650</v>
+        <v>14600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.46%</t>
+          <t>'+3.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
         <v>9.82</v>
@@ -794,7 +794,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>4889835835</v>
+        <v>6182719705</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -803,23 +803,23 @@
         <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 공매도, 주가 조작 의혹 제기로 부정적인 논조 형성. 객관적 근거 없이 하락 기대감만 표출.</t>
+          <t>외국인, 연기금 매수세 및 실적 우량주 언급. 다만, 주가 조작 관련 의혹 및 정치적 발언이 부정적 sentiment를 유발.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작', '대차']</t>
+          <t>['실적', '외국인', '연기금']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H5" t="n">
         <v>22.23</v>
@@ -886,7 +886,7 @@
         <v>22.29</v>
       </c>
       <c r="O5" t="n">
-        <v>12126904050</v>
+        <v>19173166750</v>
       </c>
       <c r="P5" t="n">
         <v>139200</v>
@@ -895,14 +895,14 @@
         <v>57000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SMR 관련 뉴스 및 데이터센터 투자 확대 가능성에 대한 기대감 존재. 그러나 반도체 대비 낮은 상승률과 정부 정책 비판으로 객관성 부족.</t>
+          <t>SMR 관련 기대감 및 미국 시간외 주가 상승 소식에 따른 두산에너빌리티 상승 언급. 다만, 정부 정책 및 개인 투자자들의 답답함 표현이 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['SMR', '데이터센터', '야간선물']</t>
+          <t>['SMR', '시간외', '개인 투자자']</t>
         </is>
       </c>
       <c r="X5" t="n">

--- a/data/trending_integrated_20261021_09.xlsx
+++ b/data/trending_integrated_20261021_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1301000</v>
+        <v>10970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+6.38%</t>
+          <t>'+12.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.04</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>800</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>497</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>2006</v>
+        <v>183</v>
       </c>
       <c r="H2" t="n">
-        <v>48.77</v>
+        <v>1.28</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1223000</v>
+        <v>9770</v>
       </c>
       <c r="K2" t="n">
-        <v>1260000</v>
+        <v>10320</v>
       </c>
       <c r="L2" t="n">
-        <v>1304000</v>
+        <v>11090</v>
       </c>
       <c r="M2" t="n">
-        <v>1258000</v>
+        <v>9690</v>
       </c>
       <c r="N2" t="n">
-        <v>48.81</v>
+        <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>930428350500</v>
+        <v>68762751275</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>11250</v>
       </c>
       <c r="Q2" t="n">
-        <v>468000</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>95000</v>
+        <v>-10000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 시간외 반도체 주가 급등 소식에 SK하이닉스 상승 기대감 형성. 솔리다임 상장 관련 언급 및 정치적 발언이 혼재.</t>
+          <t>로봇 섹터 강세와 함께 신고가 경신 기대감. 에브리봇 등 관련주 동반 급등 및 외국인 순매수 추이.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '솔리다임', '시간외']</t>
+          <t>['로봇', '신고가', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>222500</v>
+        <v>1315000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.20%</t>
+          <t>'+7.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="G3" t="n">
-        <v>3216</v>
+        <v>1714</v>
       </c>
       <c r="H3" t="n">
-        <v>46.08</v>
+        <v>48.77</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>211500</v>
+        <v>1223000</v>
       </c>
       <c r="K3" t="n">
-        <v>217000</v>
+        <v>1260000</v>
       </c>
       <c r="L3" t="n">
-        <v>223000</v>
+        <v>1316000</v>
       </c>
       <c r="M3" t="n">
-        <v>217000</v>
+        <v>1258000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.04</v>
+        <v>48.81</v>
       </c>
       <c r="O3" t="n">
-        <v>592368928000</v>
+        <v>1141740181000</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R3" t="n">
-        <v>18000</v>
+        <v>95000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 시간외 반도체 주가 급등 및 실적 호조 소식에 따른 삼성전자 상승 기대감 형성. 다만, 일부 정치적 발언이 혼재.</t>
+          <t>솔리다임 상장 관련 이슈에 따른 주가 변동성 예상. 자사주 종료일과 반대매매 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '시간외', '실적']</t>
+          <t>['솔리다임', '자사주', '반대매매']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14600</v>
+        <v>224500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.11%</t>
+          <t>'+6.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>504</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>2924</v>
       </c>
       <c r="H4" t="n">
-        <v>9.82</v>
+        <v>46.08</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14160</v>
+        <v>211500</v>
       </c>
       <c r="K4" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="L4" t="n">
-        <v>14760</v>
+        <v>224500</v>
       </c>
       <c r="M4" t="n">
-        <v>14340</v>
+        <v>217000</v>
       </c>
       <c r="N4" t="n">
-        <v>9.779999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="O4" t="n">
-        <v>6182719705</v>
+        <v>757552475000</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R4" t="n">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인, 연기금 매수세 및 실적 우량주 언급. 다만, 주가 조작 관련 의혹 및 정치적 발언이 부정적 sentiment를 유발.</t>
+          <t>미국 시간 외 반도체 주가 급등 소식에 따른 삼성전자 상승 기대감. 슈퍼마이크로 실적 호조에 따른 동반 상승 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', '외국인', '연기금']</t>
+          <t>['반도체', '시간외', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63700</v>
+        <v>14710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="H5" t="n">
-        <v>22.23</v>
+        <v>9.82</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,60 +871,244 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>62800</v>
+        <v>14160</v>
       </c>
       <c r="K5" t="n">
-        <v>63600</v>
+        <v>14340</v>
       </c>
       <c r="L5" t="n">
-        <v>64200</v>
+        <v>14760</v>
       </c>
       <c r="M5" t="n">
-        <v>62600</v>
+        <v>14340</v>
       </c>
       <c r="N5" t="n">
-        <v>22.29</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>19173166750</v>
+        <v>7695886665</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-36000</v>
+        <v>32000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SMR 관련 기대감 및 미국 시간외 주가 상승 소식에 따른 두산에너빌리티 상승 언급. 다만, 정부 정책 및 개인 투자자들의 답답함 표현이 혼재.</t>
+          <t>외인, 연기금 매수세 유입 및 실적 개선 기대감 속 목표가 5만원 제시. 주가 조작 및 뱅크런 관련 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['실적주', '외인', '연기금']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>64100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+2.07%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>74</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>170</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>62800</v>
+      </c>
+      <c r="K6" t="n">
+        <v>63600</v>
+      </c>
+      <c r="L6" t="n">
+        <v>64300</v>
+      </c>
+      <c r="M6" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="O6" t="n">
+        <v>22313138750</v>
+      </c>
+      <c r="P6" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMR 사업 관련 기대감에도 불구하고 시장 전반의 불안정성과 외인 매도세로 인한 주가 부진. 정부 정책 및 수급 불안정 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>0.2</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>['SMR', '시간외', '개인 투자자']</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['SMR', '수급', '정부정책']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17650</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+1.91%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>17320</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17480</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17820</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17340</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9258765905</v>
+      </c>
+      <c r="P7" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>17210</v>
+      </c>
+      <c r="R7" t="n">
+        <v>67000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>전반적인 시장 하락세 속에서 조선업종의 투자 매력 저하 및 부진한 주가 흐름에 대한 우려.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['조선업', '하락', '투자매력']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>010140</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261021_09.xlsx
+++ b/data/trending_integrated_20261021_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10970</v>
+        <v>10720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.28%</t>
+          <t>'+9.72%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2" t="n">
         <v>44</v>
       </c>
-      <c r="F2" t="n">
-        <v>34</v>
-      </c>
       <c r="G2" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="H2" t="n">
         <v>1.28</v>
@@ -610,7 +610,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>68762751275</v>
+        <v>86079460465</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세와 함께 신고가 경신 기대감. 에브리봇 등 관련주 동반 급등 및 외국인 순매수 추이.</t>
+          <t>로봇주 섹터 내 HT로보틱스의 신고가 및 급등 가능성에 대한 기대감. 중국 철수 및 SDI 섹터 동반 상승 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '신고가', '급등']</t>
+          <t>['로봇주', '신고가', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1315000</v>
+        <v>1317000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.52%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="G3" t="n">
-        <v>1714</v>
+        <v>1563</v>
       </c>
       <c r="H3" t="n">
         <v>48.77</v>
@@ -693,7 +693,7 @@
         <v>1260000</v>
       </c>
       <c r="L3" t="n">
-        <v>1316000</v>
+        <v>1319000</v>
       </c>
       <c r="M3" t="n">
         <v>1258000</v>
@@ -702,7 +702,7 @@
         <v>48.81</v>
       </c>
       <c r="O3" t="n">
-        <v>1141740181000</v>
+        <v>1329177818000</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 이슈에 따른 주가 변동성 예상. 자사주 종료일과 반대매매 우려.</t>
+          <t>솔리다임 상장 관련 이슈 속 SK하이닉스 170만원 이상 목표가 제시. 자사주 종료일 및 반대매매 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['솔리다임', '자사주', '반대매매']</t>
+          <t>['솔리다임', '상장', '자사주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224500</v>
+        <v>223500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.15%</t>
+          <t>'+5.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G4" t="n">
-        <v>2924</v>
+        <v>2666</v>
       </c>
       <c r="H4" t="n">
         <v>46.08</v>
@@ -785,7 +785,7 @@
         <v>217000</v>
       </c>
       <c r="L4" t="n">
-        <v>224500</v>
+        <v>224750</v>
       </c>
       <c r="M4" t="n">
         <v>217000</v>
@@ -794,7 +794,7 @@
         <v>46.04</v>
       </c>
       <c r="O4" t="n">
-        <v>757552475000</v>
+        <v>880120568250</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,12 +810,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 시간 외 반도체 주가 급등 소식에 따른 삼성전자 상승 기대감. 슈퍼마이크로 실적 호조에 따른 동반 상승 예상.</t>
+          <t>미국 시간 외 시장에서 반도체주 급등에 따른 삼성전자 상승 기대감. 슈퍼마이크로 실적 호조 및 AI 전쟁 관련 뉴스가 긍정적 요인으로 작용.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14710</v>
+        <v>14635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+3.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H5" t="n">
         <v>9.82</v>
@@ -877,7 +877,7 @@
         <v>14340</v>
       </c>
       <c r="L5" t="n">
-        <v>14760</v>
+        <v>14780</v>
       </c>
       <c r="M5" t="n">
         <v>14340</v>
@@ -886,7 +886,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>7695886665</v>
+        <v>9004082560</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인, 연기금 매수세 유입 및 실적 개선 기대감 속 목표가 5만원 제시. 주가 조작 및 뱅크런 관련 정치적 이슈 언급.</t>
+          <t>정치 관련 발언이 주를 이루며, 대우건설 자체에 대한 긍정적 언급은 부족. 외국인, 연기금 매수세 언급되나 전반적인 투자 심리는 부정적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적주', '외인', '연기금']</t>
+          <t>['이재명', '주가조작', '대차']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64100</v>
+        <v>63900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
         <v>22.23</v>
@@ -978,7 +978,7 @@
         <v>22.29</v>
       </c>
       <c r="O6" t="n">
-        <v>22313138750</v>
+        <v>25067306650</v>
       </c>
       <c r="P6" t="n">
         <v>139200</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SMR 사업 관련 기대감에도 불구하고 시장 전반의 불안정성과 외인 매도세로 인한 주가 부진. 정부 정책 및 수급 불안정 언급.</t>
+          <t>정부 정책 및 외인 매도에 대한 불만 표출. SMR 관련 기대감 있으나, 다른 종목 대비 낮은 상승률에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SMR', '수급', '정부정책']</t>
+          <t>['SMR', '정부', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17650</v>
+        <v>17590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+1.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
         <v>27.78</v>
@@ -1070,7 +1070,7 @@
         <v>27.78</v>
       </c>
       <c r="O7" t="n">
-        <v>9258765905</v>
+        <v>10321084005</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전반적인 시장 하락세 속에서 조선업종의 투자 매력 저하 및 부진한 주가 흐름에 대한 우려.</t>
+          <t>정치적 비판과 함께 조선업에 대한 부정적 전망이 지배적. 반도체 업종으로의 자금 이동 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['조선업', '하락', '투자매력']</t>
+          <t>['조선업', '반도체', '정부']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20261021_09.xlsx
+++ b/data/trending_integrated_20261021_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10720</v>
+        <v>10660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+9.72%</t>
+          <t>'+9.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="H2" t="n">
         <v>1.28</v>
@@ -610,7 +610,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>86079460465</v>
+        <v>95725715285</v>
       </c>
       <c r="P2" t="n">
         <v>11250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇주 섹터 내 HT로보틱스의 신고가 및 급등 가능성에 대한 기대감. 중국 철수 및 SDI 섹터 동반 상승 언급.</t>
+          <t>HT로보틱스의 연이은 신고가 경신 가능성에 대한 기대감과 급락 우려 공존. 로봇주 섹터 전반의 흐름 및 외국인/기관 수급 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', '급등']</t>
+          <t>['로봇주', '신고가', '수급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1317000</v>
+        <v>1299000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="G3" t="n">
-        <v>1563</v>
+        <v>1433</v>
       </c>
       <c r="H3" t="n">
         <v>48.77</v>
@@ -702,7 +702,7 @@
         <v>48.81</v>
       </c>
       <c r="O3" t="n">
-        <v>1329177818000</v>
+        <v>1497057110000</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 이슈 속 SK하이닉스 170만원 이상 목표가 제시. 자사주 종료일 및 반대매매 관련 언급.</t>
+          <t>솔리다임 상장 이슈와 마이크론 공장 파업 가능성이 SK하이닉스 주가에 영향을 미칠 것이라는 분석. 긍정적 차트 분석과 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '자사주']</t>
+          <t>['솔리다임', '파업', '차트']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>223500</v>
+        <v>222000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.67%</t>
+          <t>'+4.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G4" t="n">
-        <v>2666</v>
+        <v>2275</v>
       </c>
       <c r="H4" t="n">
         <v>46.08</v>
@@ -794,7 +794,7 @@
         <v>46.04</v>
       </c>
       <c r="O4" t="n">
-        <v>880120568250</v>
+        <v>964709638250</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 시간 외 시장에서 반도체주 급등에 따른 삼성전자 상승 기대감. 슈퍼마이크로 실적 호조 및 AI 전쟁 관련 뉴스가 긍정적 요인으로 작용.</t>
+          <t>미국 시간 외 시장 반도체주 급등 및 노무라의 파격적인 실적 전망에 따른 삼성전자 상승 기대감 고조. 일부 외인 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '시간외', '급등']</t>
+          <t>['반도체', '전망', '외인']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14635</v>
+        <v>14470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.35%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>109</v>
@@ -886,7 +886,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>9004082560</v>
+        <v>10110036280</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63900</v>
+        <v>2900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+2.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K6" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L6" t="n">
-        <v>64300</v>
+        <v>3300</v>
       </c>
       <c r="M6" t="n">
-        <v>62600</v>
+        <v>2900</v>
       </c>
       <c r="N6" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O6" t="n">
-        <v>25067306650</v>
+        <v>13582495639</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R6" t="n">
-        <v>-36000</v>
+        <v>-574000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정부 정책 및 외인 매도에 대한 불만 표출. SMR 관련 기대감 있으나, 다른 종목 대비 낮은 상승률에 대한 불만 제기.</t>
+          <t>스페이스X의 역대급 실적 발표에 따른 아주IB투자의 투자 기대감 고조. 합병 가능성 및 단기 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SMR', '정부', '외인']</t>
+          <t>['스페이스X', '실적', '합병']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17590</v>
+        <v>17420</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.56%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H7" t="n">
         <v>27.78</v>
@@ -1070,7 +1070,7 @@
         <v>27.78</v>
       </c>
       <c r="O7" t="n">
-        <v>10321084005</v>
+        <v>11841552945</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 비판과 함께 조선업에 대한 부정적 전망이 지배적. 반도체 업종으로의 자금 이동 가능성 언급.</t>
+          <t>조선업 섹터의 낮은 이익률과 반도체 섹터로의 자금 이동에 대한 부정적 전망. 주가 하락 및 부진에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['조선업', '반도체', '정부']</t>
+          <t>['조선업', '반도체', '이익률']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1109,6 +1109,98 @@
       <c r="Z7" t="inlineStr">
         <is>
           <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>63100</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+0.48%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>93</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57</v>
+      </c>
+      <c r="G8" t="n">
+        <v>205</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>62800</v>
+      </c>
+      <c r="K8" t="n">
+        <v>63600</v>
+      </c>
+      <c r="L8" t="n">
+        <v>64300</v>
+      </c>
+      <c r="M8" t="n">
+        <v>62600</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="O8" t="n">
+        <v>28055828250</v>
+      </c>
+      <c r="P8" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMR 분야에서의 두산에너빌리티의 경쟁력에 대한 언급과 함께, 타 섹터 대비 주가 상승 동력 부족에 대한 불만 표출. 시장 소외 우려.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['SMR', '경쟁력', '소외']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>
